--- a/ci-build/observations-summary.xlsx
+++ b/ci-build/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="141">
   <si>
     <t>Profile</t>
   </si>
@@ -56,7 +56,7 @@
     <t/>
   </si>
   <si>
-    <t>null#72018-2, null#241736003, null#18794-8, null#RID28536, null#300886002, null#RID3933, null#373945005, null#RID4002, null#301782006, null#RID58844</t>
+    <t>null#72018-2, null#146611000146107, null#18794-8, null#RID28536, null#290073004, null#RID3933, null#44771000, null#RID4002, null#284429001, null#RID58844</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
@@ -77,7 +77,7 @@
     <t>BIH Senologie Checkliste Erbliche Belastung</t>
   </si>
   <si>
-    <t>SNOMED CT#445039002</t>
+    <t>SNOMED CT#225338004</t>
   </si>
   <si>
     <t>booleanĵ</t>
@@ -89,6 +89,36 @@
     <t>integerĵ</t>
   </si>
   <si>
+    <t>senologie-er-status</t>
+  </si>
+  <si>
+    <t>BIH Senologie ER-Status</t>
+  </si>
+  <si>
+    <t>null#40556-3</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>SNOMED CT#1234804006</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>SNOMED CT#1236874005</t>
+  </si>
+  <si>
+    <t>CS Senologie Biomarker Erweiterungen#irs-score</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>SNOMED CT#445104009</t>
+  </si>
+  <si>
     <t>senologie-follow-up</t>
   </si>
   <si>
@@ -98,15 +128,9 @@
     <t>null#396432002</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
-  </si>
-  <si>
     <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
   </si>
   <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
     <t>SNOMED CT#445200009</t>
   </si>
   <si>
@@ -134,9 +158,6 @@
     <t>https://www.senologie.org/fhir/ValueSet/vs-senologie-genexpressionstest (required)</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
     <t>senologie-gynaekologische-anamnese</t>
   </si>
   <si>
@@ -167,16 +188,28 @@
     <t>CodeableConcept, boolean</t>
   </si>
   <si>
+    <t>senologie-her2-status</t>
+  </si>
+  <si>
+    <t>BIH Senologie HER2-Status (IHC)</t>
+  </si>
+  <si>
+    <t>null#48676-1</t>
+  </si>
+  <si>
+    <t>LOINC#85319-2</t>
+  </si>
+  <si>
+    <t>LOINC#96893-3</t>
+  </si>
+  <si>
     <t>senologie-ki67-proliferationsindex</t>
   </si>
   <si>
     <t>BIH Senologie Ki-67 Proliferationsindex</t>
   </si>
   <si>
-    <t>null#29593-1</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
+    <t>null#85330-9</t>
   </si>
   <si>
     <t>senologie-klinische-untersuchung</t>
@@ -200,7 +233,25 @@
     <t>SNOMED CT#248819006</t>
   </si>
   <si>
-    <t>SNOMED CT#301782006</t>
+    <t>SNOMED CT#284429001</t>
+  </si>
+  <si>
+    <t>SNOMED CT#46662001</t>
+  </si>
+  <si>
+    <t>SNOMED CT#366348007</t>
+  </si>
+  <si>
+    <t>SNOMED CT#248804005</t>
+  </si>
+  <si>
+    <t>SNOMED CT#399504009</t>
+  </si>
+  <si>
+    <t>SNOMED CT#399534004</t>
+  </si>
+  <si>
+    <t>SNOMED CT#363676003</t>
   </si>
   <si>
     <t>senologie-operative-komplikation</t>
@@ -252,6 +303,21 @@
   </si>
   <si>
     <t>LOINC#83053-9</t>
+  </si>
+  <si>
+    <t>senologie-pr-status</t>
+  </si>
+  <si>
+    <t>BIH Senologie PR-Status</t>
+  </si>
+  <si>
+    <t>null#85339-0</t>
+  </si>
+  <si>
+    <t>SNOMED CT#1234803000</t>
+  </si>
+  <si>
+    <t>SNOMED CT#1237278006</t>
   </si>
   <si>
     <t>senologie-somatische-mutation</t>
@@ -502,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -662,13 +728,13 @@
         <v>27</v>
       </c>
       <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>30</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -694,7 +760,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
@@ -703,7 +769,7 @@
         <v>13</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -729,7 +795,7 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
@@ -738,7 +804,7 @@
         <v>13</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -764,7 +830,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -773,7 +839,7 @@
         <v>13</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -799,7 +865,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
@@ -808,7 +874,7 @@
         <v>13</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -822,28 +888,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="C10" t="s" s="2">
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>16</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -857,10 +923,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -869,16 +935,16 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -895,7 +961,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -904,7 +970,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>13</v>
@@ -930,17 +996,17 @@
         <v>13</v>
       </c>
       <c r="B13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="C13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>46</v>
-      </c>
       <c r="F13" t="s" s="2">
         <v>13</v>
       </c>
@@ -948,7 +1014,7 @@
         <v>13</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -965,7 +1031,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>13</v>
@@ -974,7 +1040,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>13</v>
@@ -997,28 +1063,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
@@ -1032,10 +1098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -1044,16 +1110,16 @@
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>18</v>
@@ -1067,10 +1133,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>13</v>
@@ -1079,16 +1145,16 @@
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -1105,7 +1171,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -1114,7 +1180,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
@@ -1123,7 +1189,7 @@
         <v>13</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -1140,7 +1206,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1149,7 +1215,7 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
@@ -1158,7 +1224,7 @@
         <v>13</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
@@ -1175,17 +1241,17 @@
         <v>13</v>
       </c>
       <c r="B20" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="C20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>61</v>
-      </c>
       <c r="F20" t="s" s="2">
         <v>13</v>
       </c>
@@ -1193,7 +1259,7 @@
         <v>13</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1207,10 +1273,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1219,16 +1285,16 @@
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1242,10 +1308,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1254,16 +1320,16 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1280,7 +1346,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1289,7 +1355,7 @@
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>13</v>
@@ -1298,7 +1364,7 @@
         <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -1312,28 +1378,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1347,28 +1413,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="C25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1385,7 +1451,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1394,7 +1460,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1403,7 +1469,7 @@
         <v>13</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -1420,7 +1486,7 @@
         <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>13</v>
@@ -1429,7 +1495,7 @@
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>13</v>
@@ -1438,7 +1504,7 @@
         <v>13</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -1455,7 +1521,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>13</v>
@@ -1464,7 +1530,7 @@
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>13</v>
@@ -1473,7 +1539,7 @@
         <v>13</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>18</v>
@@ -1490,7 +1556,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>13</v>
@@ -1499,7 +1565,7 @@
         <v>13</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>13</v>
@@ -1508,7 +1574,7 @@
         <v>13</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -1525,7 +1591,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>13</v>
@@ -1534,7 +1600,7 @@
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>13</v>
@@ -1543,7 +1609,7 @@
         <v>13</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -1557,28 +1623,28 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -1595,7 +1661,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1604,7 +1670,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1613,7 +1679,7 @@
         <v>13</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -1630,7 +1696,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1639,7 +1705,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1648,7 +1714,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -1665,7 +1731,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1674,7 +1740,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1683,7 +1749,7 @@
         <v>13</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -1700,7 +1766,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1709,7 +1775,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>13</v>
@@ -1718,7 +1784,7 @@
         <v>13</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>18</v>
@@ -1732,7 +1798,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>81</v>
@@ -1744,16 +1810,16 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -1779,7 +1845,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1788,7 +1854,7 @@
         <v>13</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>18</v>
@@ -1802,28 +1868,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H38" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>32</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>18</v>
@@ -1840,7 +1906,7 @@
         <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1858,7 +1924,7 @@
         <v>13</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>18</v>
@@ -1875,7 +1941,7 @@
         <v>13</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>13</v>
@@ -1893,7 +1959,7 @@
         <v>13</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
@@ -1910,7 +1976,7 @@
         <v>13</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>13</v>
@@ -1928,7 +1994,7 @@
         <v>13</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>18</v>
@@ -1945,7 +2011,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>13</v>
@@ -1963,7 +2029,7 @@
         <v>13</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -1980,7 +2046,7 @@
         <v>13</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>13</v>
@@ -1998,7 +2064,7 @@
         <v>13</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>18</v>
@@ -2015,7 +2081,7 @@
         <v>13</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>13</v>
@@ -2024,7 +2090,7 @@
         <v>13</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>13</v>
@@ -2033,7 +2099,7 @@
         <v>13</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -2047,10 +2113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>13</v>
@@ -2059,16 +2125,16 @@
         <v>13</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -2085,7 +2151,7 @@
         <v>13</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>13</v>
@@ -2094,7 +2160,7 @@
         <v>13</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>13</v>
@@ -2103,7 +2169,7 @@
         <v>13</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -2120,7 +2186,7 @@
         <v>13</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>13</v>
@@ -2129,7 +2195,7 @@
         <v>13</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>13</v>
@@ -2138,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -2155,7 +2221,7 @@
         <v>13</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>13</v>
@@ -2164,7 +2230,7 @@
         <v>13</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>13</v>
@@ -2173,7 +2239,7 @@
         <v>13</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2190,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>13</v>
@@ -2199,7 +2265,7 @@
         <v>13</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>13</v>
@@ -2208,7 +2274,7 @@
         <v>13</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>18</v>
@@ -2222,28 +2288,28 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>18</v>
@@ -2260,7 +2326,7 @@
         <v>13</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>13</v>
@@ -2269,7 +2335,7 @@
         <v>13</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>13</v>
@@ -2278,7 +2344,7 @@
         <v>13</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>18</v>
@@ -2295,7 +2361,7 @@
         <v>13</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>13</v>
@@ -2304,7 +2370,7 @@
         <v>13</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>13</v>
@@ -2330,7 +2396,7 @@
         <v>13</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>13</v>
@@ -2339,7 +2405,7 @@
         <v>13</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>13</v>
@@ -2348,7 +2414,7 @@
         <v>13</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>18</v>
@@ -2365,7 +2431,7 @@
         <v>13</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>13</v>
@@ -2374,7 +2440,7 @@
         <v>13</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>13</v>
@@ -2383,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>18</v>
@@ -2400,7 +2466,7 @@
         <v>13</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>13</v>
@@ -2409,7 +2475,7 @@
         <v>13</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>13</v>
@@ -2418,7 +2484,7 @@
         <v>13</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -2435,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>13</v>
@@ -2444,7 +2510,7 @@
         <v>13</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>13</v>
@@ -2453,7 +2519,7 @@
         <v>13</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>18</v>
@@ -2470,7 +2536,7 @@
         <v>13</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>13</v>
@@ -2479,7 +2545,7 @@
         <v>13</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>13</v>
@@ -2488,7 +2554,7 @@
         <v>13</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>18</v>
@@ -2505,7 +2571,7 @@
         <v>13</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>13</v>
@@ -2514,7 +2580,7 @@
         <v>13</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>13</v>
@@ -2523,7 +2589,7 @@
         <v>13</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>18</v>
@@ -2540,7 +2606,7 @@
         <v>13</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>13</v>
@@ -2549,7 +2615,7 @@
         <v>13</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>13</v>
@@ -2558,7 +2624,7 @@
         <v>13</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>18</v>
@@ -2575,7 +2641,7 @@
         <v>13</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>13</v>
@@ -2584,7 +2650,7 @@
         <v>13</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>13</v>
@@ -2593,7 +2659,7 @@
         <v>13</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -2610,7 +2676,7 @@
         <v>13</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>13</v>
@@ -2619,7 +2685,7 @@
         <v>13</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>13</v>
@@ -2645,7 +2711,7 @@
         <v>13</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>13</v>
@@ -2654,7 +2720,7 @@
         <v>13</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>13</v>
@@ -2663,7 +2729,7 @@
         <v>13</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>18</v>
@@ -2680,7 +2746,7 @@
         <v>13</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>13</v>
@@ -2689,7 +2755,7 @@
         <v>13</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>13</v>
@@ -2698,7 +2764,7 @@
         <v>13</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
@@ -2715,7 +2781,7 @@
         <v>13</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>13</v>
@@ -2724,24 +2790,689 @@
         <v>13</v>
       </c>
       <c r="E64" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H64" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="F64" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H64" t="s" s="2">
+      <c r="I64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H65" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K64" t="s" s="2">
+      <c r="I65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K83" t="s" s="2">
         <v>13</v>
       </c>
     </row>
